--- a/oa name resolution threshold check.xlsx
+++ b/oa name resolution threshold check.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tmitconsultinginc-my.sharepoint.com/personal/tania_tmit_ca/Documents/Documents/juan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="265" documentId="8_{B977C1F8-4701-4AC5-818F-9599233F245C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{814F7413-CAC5-4B3C-9939-37CAEFD2AB35}"/>
+  <xr:revisionPtr revIDLastSave="271" documentId="8_{B977C1F8-4701-4AC5-818F-9599233F245C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CCE7EBF-8170-47C1-BB70-C118447D949F}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="7" xr2:uid="{ECC1C6B3-E555-425F-9656-7FEB29A2B553}"/>
+    <workbookView xWindow="28690" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{ECC1C6B3-E555-425F-9656-7FEB29A2B553}"/>
   </bookViews>
   <sheets>
     <sheet name="75" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,10 @@
     <sheet name="90" sheetId="7" r:id="rId7"/>
     <sheet name="comparisons" sheetId="8" r:id="rId8"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'75'!$A$1:$F$509</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'85'!$A$1:$F$159</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +47,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -4770,7 +4774,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-CA"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -5238,7 +5242,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-CA"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -17354,6 +17358,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F509" xr:uid="{9E8B19A0-0C69-4D80-851A-5A8411449AD2}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -38573,6 +38578,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F159" xr:uid="{0429794E-1E1C-438D-B836-4A28B95599C9}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/oa name resolution threshold check.xlsx
+++ b/oa name resolution threshold check.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tmitconsultinginc-my.sharepoint.com/personal/tania_tmit_ca/Documents/Documents/juan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="271" documentId="8_{B977C1F8-4701-4AC5-818F-9599233F245C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CCE7EBF-8170-47C1-BB70-C118447D949F}"/>
+  <xr:revisionPtr revIDLastSave="272" documentId="8_{B977C1F8-4701-4AC5-818F-9599233F245C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A91D0787-2140-4DFE-AB6F-07DC6F6F960C}"/>
   <bookViews>
-    <workbookView xWindow="28690" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{ECC1C6B3-E555-425F-9656-7FEB29A2B553}"/>
+    <workbookView xWindow="-83" yWindow="-83" windowWidth="21766" windowHeight="13846" xr2:uid="{ECC1C6B3-E555-425F-9656-7FEB29A2B553}"/>
   </bookViews>
   <sheets>
     <sheet name="75" sheetId="1" r:id="rId1"/>
@@ -7146,6 +7146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8B19A0-0C69-4D80-851A-5A8411449AD2}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J509"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -7206,7 +7207,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -7237,7 +7238,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -7257,7 +7258,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -7297,7 +7298,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -7317,7 +7318,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -7337,7 +7338,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -7357,7 +7358,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -7397,7 +7398,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -7417,7 +7418,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -7457,7 +7458,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -7477,7 +7478,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -7517,7 +7518,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -7557,7 +7558,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -7577,7 +7578,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>65</v>
       </c>
@@ -7597,7 +7598,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>69</v>
       </c>
@@ -7637,7 +7638,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -7657,7 +7658,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>79</v>
       </c>
@@ -7677,7 +7678,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>79</v>
       </c>
@@ -7737,7 +7738,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>93</v>
       </c>
@@ -7797,7 +7798,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>105</v>
       </c>
@@ -7817,7 +7818,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>109</v>
       </c>
@@ -7837,7 +7838,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>113</v>
       </c>
@@ -7897,7 +7898,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>125</v>
       </c>
@@ -7917,7 +7918,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>129</v>
       </c>
@@ -7977,7 +7978,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>141</v>
       </c>
@@ -7997,7 +7998,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>145</v>
       </c>
@@ -8057,7 +8058,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>83</v>
       </c>
@@ -8157,7 +8158,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>175</v>
       </c>
@@ -8177,7 +8178,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>179</v>
       </c>
@@ -8197,7 +8198,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>183</v>
       </c>
@@ -8217,7 +8218,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>183</v>
       </c>
@@ -8237,7 +8238,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>183</v>
       </c>
@@ -8317,7 +8318,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>201</v>
       </c>
@@ -8337,7 +8338,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>201</v>
       </c>
@@ -8357,7 +8358,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>201</v>
       </c>
@@ -8397,7 +8398,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>201</v>
       </c>
@@ -8417,7 +8418,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>201</v>
       </c>
@@ -8437,7 +8438,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>201</v>
       </c>
@@ -8457,7 +8458,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>211</v>
       </c>
@@ -8477,7 +8478,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>211</v>
       </c>
@@ -8557,7 +8558,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>223</v>
       </c>
@@ -8597,7 +8598,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>202</v>
       </c>
@@ -8617,7 +8618,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>231</v>
       </c>
@@ -8697,7 +8698,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>245</v>
       </c>
@@ -8717,7 +8718,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>249</v>
       </c>
@@ -8737,7 +8738,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>253</v>
       </c>
@@ -8757,7 +8758,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>253</v>
       </c>
@@ -8777,7 +8778,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>259</v>
       </c>
@@ -8797,7 +8798,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>259</v>
       </c>
@@ -8817,7 +8818,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>205</v>
       </c>
@@ -8837,7 +8838,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>205</v>
       </c>
@@ -8857,7 +8858,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>205</v>
       </c>
@@ -8877,7 +8878,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>207</v>
       </c>
@@ -8897,7 +8898,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>265</v>
       </c>
@@ -8917,7 +8918,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>269</v>
       </c>
@@ -8937,7 +8938,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>232</v>
       </c>
@@ -8957,7 +8958,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>232</v>
       </c>
@@ -8997,7 +8998,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>279</v>
       </c>
@@ -9037,7 +9038,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>285</v>
       </c>
@@ -9057,7 +9058,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>266</v>
       </c>
@@ -9097,7 +9098,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>260</v>
       </c>
@@ -9117,7 +9118,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>295</v>
       </c>
@@ -9157,7 +9158,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>299</v>
       </c>
@@ -9237,7 +9238,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>311</v>
       </c>
@@ -9257,7 +9258,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>184</v>
       </c>
@@ -9277,7 +9278,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>209</v>
       </c>
@@ -9297,7 +9298,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>315</v>
       </c>
@@ -9377,7 +9378,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>331</v>
       </c>
@@ -9397,7 +9398,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>335</v>
       </c>
@@ -9457,7 +9458,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>345</v>
       </c>
@@ -9517,7 +9518,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>357</v>
       </c>
@@ -9557,7 +9558,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>361</v>
       </c>
@@ -9617,7 +9618,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>373</v>
       </c>
@@ -9677,7 +9678,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>385</v>
       </c>
@@ -9737,7 +9738,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>397</v>
       </c>
@@ -9777,7 +9778,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>405</v>
       </c>
@@ -9797,7 +9798,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>407</v>
       </c>
@@ -9837,7 +9838,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>415</v>
       </c>
@@ -9897,7 +9898,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>427</v>
       </c>
@@ -9917,7 +9918,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>431</v>
       </c>
@@ -9977,7 +9978,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>441</v>
       </c>
@@ -9997,7 +9998,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>445</v>
       </c>
@@ -10057,7 +10058,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>453</v>
       </c>
@@ -10157,7 +10158,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>475</v>
       </c>
@@ -10197,7 +10198,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>483</v>
       </c>
@@ -10217,7 +10218,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>487</v>
       </c>
@@ -10357,7 +10358,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>513</v>
       </c>
@@ -10377,7 +10378,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>517</v>
       </c>
@@ -10397,7 +10398,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>521</v>
       </c>
@@ -10457,7 +10458,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>533</v>
       </c>
@@ -10477,7 +10478,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>533</v>
       </c>
@@ -10537,7 +10538,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>543</v>
       </c>
@@ -10557,7 +10558,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>547</v>
       </c>
@@ -10577,7 +10578,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>551</v>
       </c>
@@ -10597,7 +10598,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>553</v>
       </c>
@@ -10617,7 +10618,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>554</v>
       </c>
@@ -10637,7 +10638,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>559</v>
       </c>
@@ -10677,7 +10678,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>567</v>
       </c>
@@ -10717,7 +10718,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>575</v>
       </c>
@@ -10777,7 +10778,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>585</v>
       </c>
@@ -10797,7 +10798,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>560</v>
       </c>
@@ -10837,7 +10838,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>591</v>
       </c>
@@ -10897,7 +10898,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>603</v>
       </c>
@@ -10917,7 +10918,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>607</v>
       </c>
@@ -10957,7 +10958,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>613</v>
       </c>
@@ -10997,7 +10998,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>619</v>
       </c>
@@ -11017,7 +11018,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>623</v>
       </c>
@@ -11057,7 +11058,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>631</v>
       </c>
@@ -11077,7 +11078,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>635</v>
       </c>
@@ -11097,7 +11098,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>635</v>
       </c>
@@ -11197,7 +11198,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>653</v>
       </c>
@@ -11217,7 +11218,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>657</v>
       </c>
@@ -11237,7 +11238,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>661</v>
       </c>
@@ -11257,7 +11258,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>665</v>
       </c>
@@ -11277,7 +11278,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>669</v>
       </c>
@@ -11297,7 +11298,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>673</v>
       </c>
@@ -11377,7 +11378,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>689</v>
       </c>
@@ -11457,7 +11458,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>705</v>
       </c>
@@ -11497,7 +11498,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>713</v>
       </c>
@@ -11517,7 +11518,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>713</v>
       </c>
@@ -11537,7 +11538,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>713</v>
       </c>
@@ -11557,7 +11558,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>713</v>
       </c>
@@ -11577,7 +11578,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>723</v>
       </c>
@@ -11597,7 +11598,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>723</v>
       </c>
@@ -11617,7 +11618,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>723</v>
       </c>
@@ -11637,7 +11638,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>731</v>
       </c>
@@ -11657,7 +11658,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>731</v>
       </c>
@@ -11677,7 +11678,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>737</v>
       </c>
@@ -11697,7 +11698,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>737</v>
       </c>
@@ -11717,7 +11718,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>743</v>
       </c>
@@ -11737,7 +11738,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>743</v>
       </c>
@@ -11757,7 +11758,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>749</v>
       </c>
@@ -11817,7 +11818,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>757</v>
       </c>
@@ -11837,7 +11838,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
         <v>724</v>
       </c>
@@ -11857,7 +11858,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
         <v>724</v>
       </c>
@@ -11937,7 +11938,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
         <v>771</v>
       </c>
@@ -11957,7 +11958,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
         <v>775</v>
       </c>
@@ -11977,7 +11978,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
         <v>779</v>
       </c>
@@ -11997,7 +11998,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
         <v>779</v>
       </c>
@@ -12017,7 +12018,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
         <v>785</v>
       </c>
@@ -12057,7 +12058,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
         <v>791</v>
       </c>
@@ -12097,7 +12098,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
         <v>780</v>
       </c>
@@ -12117,7 +12118,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
         <v>801</v>
       </c>
@@ -12137,7 +12138,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
         <v>744</v>
       </c>
@@ -12157,7 +12158,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
         <v>744</v>
       </c>
@@ -12177,7 +12178,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>809</v>
       </c>
@@ -12197,7 +12198,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>738</v>
       </c>
@@ -12217,7 +12218,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
         <v>811</v>
       </c>
@@ -12237,7 +12238,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
         <v>802</v>
       </c>
@@ -12257,7 +12258,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
         <v>817</v>
       </c>
@@ -12277,7 +12278,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
         <v>805</v>
       </c>
@@ -12297,7 +12298,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
         <v>805</v>
       </c>
@@ -12317,7 +12318,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
         <v>821</v>
       </c>
@@ -12337,7 +12338,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
         <v>825</v>
       </c>
@@ -12357,7 +12358,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
         <v>807</v>
       </c>
@@ -12377,7 +12378,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
         <v>831</v>
       </c>
@@ -12417,7 +12418,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
         <v>714</v>
       </c>
@@ -12457,7 +12458,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>843</v>
       </c>
@@ -12477,7 +12478,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>847</v>
       </c>
@@ -12497,7 +12498,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
         <v>847</v>
       </c>
@@ -12517,7 +12518,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
         <v>847</v>
       </c>
@@ -12577,7 +12578,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
         <v>863</v>
       </c>
@@ -12597,7 +12598,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
         <v>867</v>
       </c>
@@ -12617,7 +12618,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
         <v>869</v>
       </c>
@@ -12657,7 +12658,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
         <v>877</v>
       </c>
@@ -12677,7 +12678,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
         <v>881</v>
       </c>
@@ -12717,7 +12718,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
         <v>851</v>
       </c>
@@ -12737,7 +12738,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
         <v>851</v>
       </c>
@@ -12757,7 +12758,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
         <v>885</v>
       </c>
@@ -12777,7 +12778,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
         <v>889</v>
       </c>
@@ -12797,7 +12798,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
         <v>856</v>
       </c>
@@ -12837,7 +12838,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
         <v>897</v>
       </c>
@@ -12857,7 +12858,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
         <v>901</v>
       </c>
@@ -12877,7 +12878,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
         <v>905</v>
       </c>
@@ -12917,7 +12918,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
         <v>911</v>
       </c>
@@ -12957,7 +12958,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
         <v>853</v>
       </c>
@@ -13017,7 +13018,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
         <v>927</v>
       </c>
@@ -13057,7 +13058,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
         <v>840</v>
       </c>
@@ -13077,7 +13078,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
         <v>937</v>
       </c>
@@ -13097,7 +13098,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
         <v>941</v>
       </c>
@@ -13277,7 +13278,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A306" t="s">
         <v>969</v>
       </c>
@@ -13357,7 +13358,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
         <v>981</v>
       </c>
@@ -13377,7 +13378,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A311" t="s">
         <v>981</v>
       </c>
@@ -13417,7 +13418,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
         <v>982</v>
       </c>
@@ -13437,7 +13438,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A314" t="s">
         <v>982</v>
       </c>
@@ -13457,7 +13458,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A315" t="s">
         <v>993</v>
       </c>
@@ -13497,7 +13498,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A317" t="s">
         <v>1001</v>
       </c>
@@ -13517,7 +13518,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
         <v>1001</v>
       </c>
@@ -13557,7 +13558,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
         <v>1011</v>
       </c>
@@ -13577,7 +13578,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
         <v>1015</v>
       </c>
@@ -13617,7 +13618,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
         <v>987</v>
       </c>
@@ -13777,7 +13778,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
         <v>1041</v>
       </c>
@@ -13917,7 +13918,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A338" t="s">
         <v>1061</v>
       </c>
@@ -13937,7 +13938,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
         <v>1065</v>
       </c>
@@ -14017,7 +14018,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
         <v>1081</v>
       </c>
@@ -14077,7 +14078,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A346" t="s">
         <v>1093</v>
       </c>
@@ -14117,7 +14118,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A348" t="s">
         <v>1101</v>
       </c>
@@ -14137,7 +14138,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
         <v>1105</v>
       </c>
@@ -14237,7 +14238,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A354" t="s">
         <v>1125</v>
       </c>
@@ -14257,7 +14258,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
         <v>1125</v>
       </c>
@@ -14277,7 +14278,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A356" t="s">
         <v>1125</v>
       </c>
@@ -14297,7 +14298,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A357" t="s">
         <v>1133</v>
       </c>
@@ -14337,7 +14338,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A359" t="s">
         <v>1141</v>
       </c>
@@ -14357,7 +14358,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A360" t="s">
         <v>1145</v>
       </c>
@@ -14377,7 +14378,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
         <v>1149</v>
       </c>
@@ -14397,7 +14398,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A362" t="s">
         <v>1153</v>
       </c>
@@ -14417,7 +14418,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A363" t="s">
         <v>1129</v>
       </c>
@@ -14437,7 +14438,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A364" t="s">
         <v>1157</v>
       </c>
@@ -14497,7 +14498,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
         <v>1169</v>
       </c>
@@ -14517,7 +14518,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A368" t="s">
         <v>1173</v>
       </c>
@@ -14537,7 +14538,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
         <v>1177</v>
       </c>
@@ -14557,7 +14558,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
         <v>1181</v>
       </c>
@@ -14577,7 +14578,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A371" t="s">
         <v>1181</v>
       </c>
@@ -14597,7 +14598,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A372" t="s">
         <v>1185</v>
       </c>
@@ -14637,7 +14638,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A374" t="s">
         <v>1193</v>
       </c>
@@ -14657,7 +14658,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A375" t="s">
         <v>1197</v>
       </c>
@@ -14677,7 +14678,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
         <v>1201</v>
       </c>
@@ -14737,7 +14738,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
         <v>1213</v>
       </c>
@@ -14757,7 +14758,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A380" t="s">
         <v>1215</v>
       </c>
@@ -14877,7 +14878,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A386" t="s">
         <v>1235</v>
       </c>
@@ -14917,7 +14918,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
         <v>1243</v>
       </c>
@@ -14977,7 +14978,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A391" t="s">
         <v>1255</v>
       </c>
@@ -14997,7 +14998,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A392" t="s">
         <v>1244</v>
       </c>
@@ -15037,7 +15038,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
         <v>1265</v>
       </c>
@@ -15057,7 +15058,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A395" t="s">
         <v>1269</v>
       </c>
@@ -15097,7 +15098,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
         <v>1277</v>
       </c>
@@ -15137,7 +15138,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A399" t="s">
         <v>1285</v>
       </c>
@@ -15157,7 +15158,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A400" t="s">
         <v>1289</v>
       </c>
@@ -15197,7 +15198,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A402" t="s">
         <v>1293</v>
       </c>
@@ -15217,7 +15218,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
         <v>1299</v>
       </c>
@@ -15237,7 +15238,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A404" t="s">
         <v>1303</v>
       </c>
@@ -15257,7 +15258,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A405" t="s">
         <v>1307</v>
       </c>
@@ -15277,7 +15278,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
         <v>1307</v>
       </c>
@@ -15297,7 +15298,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A407" t="s">
         <v>1307</v>
       </c>
@@ -15317,7 +15318,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A408" t="s">
         <v>1307</v>
       </c>
@@ -15337,7 +15338,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
         <v>1307</v>
       </c>
@@ -15357,7 +15358,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A410" t="s">
         <v>1307</v>
       </c>
@@ -15377,7 +15378,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A411" t="s">
         <v>1307</v>
       </c>
@@ -15397,7 +15398,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
         <v>1307</v>
       </c>
@@ -15417,7 +15418,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A413" t="s">
         <v>1325</v>
       </c>
@@ -15457,7 +15458,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
         <v>1333</v>
       </c>
@@ -15477,7 +15478,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A416" t="s">
         <v>1333</v>
       </c>
@@ -15497,7 +15498,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
         <v>1333</v>
       </c>
@@ -15517,7 +15518,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A418" t="s">
         <v>1333</v>
       </c>
@@ -15537,7 +15538,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A419" t="s">
         <v>1339</v>
       </c>
@@ -15557,7 +15558,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A420" t="s">
         <v>1339</v>
       </c>
@@ -15597,7 +15598,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A422" t="s">
         <v>1347</v>
       </c>
@@ -15617,7 +15618,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A423" t="s">
         <v>1334</v>
       </c>
@@ -15637,7 +15638,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
         <v>1334</v>
       </c>
@@ -15657,7 +15658,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
         <v>1353</v>
       </c>
@@ -15677,7 +15678,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A426" t="s">
         <v>1355</v>
       </c>
@@ -15717,7 +15718,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A428" t="s">
         <v>1361</v>
       </c>
@@ -15737,7 +15738,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A429" t="s">
         <v>1365</v>
       </c>
@@ -15757,7 +15758,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
         <v>1369</v>
       </c>
@@ -15797,7 +15798,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A432" t="s">
         <v>1308</v>
       </c>
@@ -15817,7 +15818,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
         <v>1308</v>
       </c>
@@ -15837,7 +15838,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A434" t="s">
         <v>1308</v>
       </c>
@@ -15857,7 +15858,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A435" t="s">
         <v>1308</v>
       </c>
@@ -15877,7 +15878,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A436" t="s">
         <v>1308</v>
       </c>
@@ -15897,7 +15898,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A437" t="s">
         <v>1308</v>
       </c>
@@ -15917,7 +15918,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A438" t="s">
         <v>1379</v>
       </c>
@@ -15937,7 +15938,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
         <v>1311</v>
       </c>
@@ -15957,7 +15958,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A440" t="s">
         <v>1311</v>
       </c>
@@ -15977,7 +15978,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A441" t="s">
         <v>1311</v>
       </c>
@@ -15997,7 +15998,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
         <v>1311</v>
       </c>
@@ -16037,7 +16038,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A444" t="s">
         <v>1311</v>
       </c>
@@ -16057,7 +16058,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A445" t="s">
         <v>1313</v>
       </c>
@@ -16077,7 +16078,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A446" t="s">
         <v>1313</v>
       </c>
@@ -16097,7 +16098,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A447" t="s">
         <v>1313</v>
       </c>
@@ -16117,7 +16118,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
         <v>1313</v>
       </c>
@@ -16157,7 +16158,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A450" t="s">
         <v>1315</v>
       </c>
@@ -16177,7 +16178,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
         <v>1315</v>
       </c>
@@ -16197,7 +16198,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A452" t="s">
         <v>1315</v>
       </c>
@@ -16237,7 +16238,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
         <v>1389</v>
       </c>
@@ -16257,7 +16258,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A455" t="s">
         <v>1317</v>
       </c>
@@ -16277,7 +16278,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
         <v>1317</v>
       </c>
@@ -16297,7 +16298,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
         <v>1319</v>
       </c>
@@ -16317,7 +16318,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A458" t="s">
         <v>1319</v>
       </c>
@@ -16357,7 +16358,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
         <v>1395</v>
       </c>
@@ -16377,7 +16378,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A461" t="s">
         <v>1323</v>
       </c>
@@ -16397,7 +16398,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A462" t="s">
         <v>1359</v>
       </c>
@@ -16497,7 +16498,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A467" t="s">
         <v>1413</v>
       </c>
@@ -16517,7 +16518,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A468" t="s">
         <v>1413</v>
       </c>
@@ -16537,7 +16538,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
         <v>1419</v>
       </c>
@@ -16557,7 +16558,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A470" t="s">
         <v>1423</v>
       </c>
@@ -16577,7 +16578,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A471" t="s">
         <v>1427</v>
       </c>
@@ -16597,7 +16598,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A472" t="s">
         <v>1414</v>
       </c>
@@ -16617,7 +16618,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A473" t="s">
         <v>1414</v>
       </c>
@@ -16637,7 +16638,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A474" t="s">
         <v>1433</v>
       </c>
@@ -16657,7 +16658,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A475" t="s">
         <v>1437</v>
       </c>
@@ -16737,7 +16738,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A479" t="s">
         <v>1445</v>
       </c>
@@ -16757,7 +16758,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A480" t="s">
         <v>1431</v>
       </c>
@@ -16777,7 +16778,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A481" t="s">
         <v>1449</v>
       </c>
@@ -16797,7 +16798,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A482" t="s">
         <v>1449</v>
       </c>
@@ -16817,7 +16818,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A483" t="s">
         <v>1449</v>
       </c>
@@ -16837,7 +16838,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="484" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A484" t="s">
         <v>1449</v>
       </c>
@@ -16857,7 +16858,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A485" t="s">
         <v>1449</v>
       </c>
@@ -16877,7 +16878,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="486" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A486" t="s">
         <v>1449</v>
       </c>
@@ -16897,7 +16898,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="487" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
         <v>1463</v>
       </c>
@@ -16917,7 +16918,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A488" t="s">
         <v>1463</v>
       </c>
@@ -16937,7 +16938,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
         <v>1463</v>
       </c>
@@ -16957,7 +16958,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
         <v>1471</v>
       </c>
@@ -16997,7 +16998,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A492" t="s">
         <v>1464</v>
       </c>
@@ -17017,7 +17018,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A493" t="s">
         <v>1479</v>
       </c>
@@ -17057,7 +17058,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A495" t="s">
         <v>1485</v>
       </c>
@@ -17077,7 +17078,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
         <v>1485</v>
       </c>
@@ -17097,7 +17098,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
         <v>1450</v>
       </c>
@@ -17117,7 +17118,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A498" t="s">
         <v>1450</v>
       </c>
@@ -17137,7 +17138,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A499" t="s">
         <v>1450</v>
       </c>
@@ -17157,7 +17158,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A500" t="s">
         <v>1491</v>
       </c>
@@ -17177,7 +17178,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A501" t="s">
         <v>1492</v>
       </c>
@@ -17197,7 +17198,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A502" t="s">
         <v>1486</v>
       </c>
@@ -17217,7 +17218,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A503" t="s">
         <v>1455</v>
       </c>
@@ -17237,7 +17238,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A504" t="s">
         <v>1455</v>
       </c>
@@ -17257,7 +17258,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
         <v>1499</v>
       </c>
@@ -17277,7 +17278,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A506" t="s">
         <v>1503</v>
       </c>
@@ -17317,7 +17318,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A508" t="s">
         <v>1457</v>
       </c>
@@ -17337,7 +17338,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A509" t="s">
         <v>1457</v>
       </c>
@@ -17358,7 +17359,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F509" xr:uid="{9E8B19A0-0C69-4D80-851A-5A8411449AD2}"/>
+  <autoFilter ref="A1:F509" xr:uid="{9E8B19A0-0C69-4D80-851A-5A8411449AD2}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="ok"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
